--- a/artfynd/A 30345-2024 artfynd.xlsx
+++ b/artfynd/A 30345-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,6 +902,2761 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121515987</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>594417</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7183674</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121515975</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90731</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>594384</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7183540</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121515980</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>594371</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7183569</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121515972</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>594435</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7183446</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121515976</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>594384</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7183540</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121515990</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56569</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>594387</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7183779</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121515977</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>594385</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7183550</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121515994</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>594343</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7183730</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121515982</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>594371</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7183569</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121515970</v>
+      </c>
+      <c r="B13" t="n">
+        <v>82391</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>594437</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7183445</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121515983</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>594375</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7183570</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121515991</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57465</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>594387</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7183695</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121515988</v>
+      </c>
+      <c r="B16" t="n">
+        <v>82391</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>594414</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7183678</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121515986</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>594413</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7183672</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121515974</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>594385</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7183523</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121515978</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>594389</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7183552</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121515979</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>594372</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7183568</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121515993</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>594381</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7183690</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121515996</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>594372</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7183791</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121515989</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>594414</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7183679</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121515985</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>594428</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7183633</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121515995</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>594345</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7183736</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121515984</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>594440</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7183609</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121515973</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>594401</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7183475</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30345-2024 artfynd.xlsx
+++ b/artfynd/A 30345-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515987</v>
+        <v>121515978</v>
       </c>
       <c r="B4" t="n">
         <v>57354</v>
@@ -940,7 +940,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594417</v>
+        <v>594389</v>
       </c>
       <c r="R4" t="n">
-        <v>7183674</v>
+        <v>7183552</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515975</v>
+        <v>121515990</v>
       </c>
       <c r="B5" t="n">
-        <v>90731</v>
+        <v>56569</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,38 +1033,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594384</v>
+        <v>594387</v>
       </c>
       <c r="R5" t="n">
-        <v>7183540</v>
+        <v>7183779</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515980</v>
+        <v>121515995</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1153,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594371</v>
+        <v>594345</v>
       </c>
       <c r="R6" t="n">
-        <v>7183569</v>
+        <v>7183736</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1254,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515972</v>
+        <v>121515996</v>
       </c>
       <c r="B7" t="n">
         <v>78607</v>
@@ -1285,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594435</v>
+        <v>594372</v>
       </c>
       <c r="R7" t="n">
-        <v>7183446</v>
+        <v>7183791</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515976</v>
+        <v>121515985</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,34 +1382,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594384</v>
+        <v>594428</v>
       </c>
       <c r="R8" t="n">
-        <v>7183540</v>
+        <v>7183633</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515990</v>
+        <v>121515983</v>
       </c>
       <c r="B9" t="n">
-        <v>56569</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,30 +1495,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102613</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1513,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594387</v>
+        <v>594375</v>
       </c>
       <c r="R9" t="n">
-        <v>7183779</v>
+        <v>7183570</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1548,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515977</v>
+        <v>121515989</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,39 +1615,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594385</v>
+        <v>594414</v>
       </c>
       <c r="R10" t="n">
-        <v>7183550</v>
+        <v>7183679</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1665,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515994</v>
+        <v>121515982</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,34 +1727,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594343</v>
+        <v>594371</v>
       </c>
       <c r="R11" t="n">
-        <v>7183730</v>
+        <v>7183569</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1777,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515982</v>
+        <v>121515972</v>
       </c>
       <c r="B12" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,39 +1844,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594371</v>
+        <v>594435</v>
       </c>
       <c r="R12" t="n">
-        <v>7183569</v>
+        <v>7183446</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1894,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515970</v>
+        <v>121515986</v>
       </c>
       <c r="B13" t="n">
-        <v>82391</v>
+        <v>57354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,34 +1956,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594437</v>
+        <v>594413</v>
       </c>
       <c r="R13" t="n">
-        <v>7183445</v>
+        <v>7183672</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2006,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2016,7 +2030,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515983</v>
+        <v>121515974</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,38 +2073,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594375</v>
+        <v>594385</v>
       </c>
       <c r="R14" t="n">
-        <v>7183570</v>
+        <v>7183523</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2122,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2132,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,10 +2169,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515991</v>
+        <v>121515977</v>
       </c>
       <c r="B15" t="n">
-        <v>57465</v>
+        <v>57354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,20 +2181,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2192,9 +2202,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2203,10 +2214,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594387</v>
+        <v>594385</v>
       </c>
       <c r="R15" t="n">
-        <v>7183695</v>
+        <v>7183550</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2238,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2248,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,10 +2286,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515988</v>
+        <v>121515994</v>
       </c>
       <c r="B16" t="n">
-        <v>82391</v>
+        <v>78607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,21 +2302,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2315,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594414</v>
+        <v>594343</v>
       </c>
       <c r="R16" t="n">
-        <v>7183678</v>
+        <v>7183730</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2350,7 +2361,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2360,7 +2371,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,10 +2398,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515986</v>
+        <v>121515980</v>
       </c>
       <c r="B17" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2403,39 +2414,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594413</v>
+        <v>594371</v>
       </c>
       <c r="R17" t="n">
-        <v>7183672</v>
+        <v>7183569</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2467,7 +2473,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2483,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,10 +2510,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515974</v>
+        <v>121515987</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2520,34 +2526,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594385</v>
+        <v>594417</v>
       </c>
       <c r="R18" t="n">
-        <v>7183523</v>
+        <v>7183674</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2579,7 +2590,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2589,7 +2600,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,7 +2627,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515978</v>
+        <v>121515984</v>
       </c>
       <c r="B19" t="n">
         <v>57354</v>
@@ -2652,7 +2663,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2661,10 +2672,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594389</v>
+        <v>594440</v>
       </c>
       <c r="R19" t="n">
-        <v>7183552</v>
+        <v>7183609</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2696,7 +2707,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,7 +2717,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,10 +2744,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515979</v>
+        <v>121515988</v>
       </c>
       <c r="B20" t="n">
-        <v>57354</v>
+        <v>82391</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2749,39 +2760,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594372</v>
+        <v>594414</v>
       </c>
       <c r="R20" t="n">
-        <v>7183568</v>
+        <v>7183678</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2813,7 +2819,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2823,7 +2829,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2850,10 +2856,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515993</v>
+        <v>121515970</v>
       </c>
       <c r="B21" t="n">
-        <v>57354</v>
+        <v>82391</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2866,39 +2872,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594381</v>
+        <v>594437</v>
       </c>
       <c r="R21" t="n">
-        <v>7183690</v>
+        <v>7183445</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2930,7 +2931,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2940,7 +2941,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2967,10 +2968,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515996</v>
+        <v>121515973</v>
       </c>
       <c r="B22" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2983,34 +2984,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594372</v>
+        <v>594401</v>
       </c>
       <c r="R22" t="n">
-        <v>7183791</v>
+        <v>7183475</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3042,7 +3048,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3052,7 +3058,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,7 +3085,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515989</v>
+        <v>121515976</v>
       </c>
       <c r="B23" t="n">
         <v>78607</v>
@@ -3119,10 +3125,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594414</v>
+        <v>594384</v>
       </c>
       <c r="R23" t="n">
-        <v>7183679</v>
+        <v>7183540</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3154,7 +3160,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3164,7 +3170,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3191,10 +3197,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515985</v>
+        <v>121515975</v>
       </c>
       <c r="B24" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3207,39 +3213,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594428</v>
+        <v>594384</v>
       </c>
       <c r="R24" t="n">
-        <v>7183633</v>
+        <v>7183540</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3271,7 +3272,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3281,7 +3282,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3308,7 +3309,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515995</v>
+        <v>121515993</v>
       </c>
       <c r="B25" t="n">
         <v>57354</v>
@@ -3344,7 +3345,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3353,10 +3354,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594345</v>
+        <v>594381</v>
       </c>
       <c r="R25" t="n">
-        <v>7183736</v>
+        <v>7183690</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3388,7 +3389,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3398,7 +3399,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3425,10 +3426,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515984</v>
+        <v>121515991</v>
       </c>
       <c r="B26" t="n">
-        <v>57354</v>
+        <v>57465</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3437,20 +3438,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3458,10 +3459,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594440</v>
+        <v>594387</v>
       </c>
       <c r="R26" t="n">
-        <v>7183609</v>
+        <v>7183695</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,7 +3542,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515973</v>
+        <v>121515979</v>
       </c>
       <c r="B27" t="n">
         <v>57354</v>
@@ -3578,7 +3578,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594401</v>
+        <v>594372</v>
       </c>
       <c r="R27" t="n">
-        <v>7183475</v>
+        <v>7183568</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 30345-2024 artfynd.xlsx
+++ b/artfynd/A 30345-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515978</v>
+        <v>121515979</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594389</v>
+        <v>594372</v>
       </c>
       <c r="R4" t="n">
-        <v>7183552</v>
+        <v>7183568</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515990</v>
+        <v>121515995</v>
       </c>
       <c r="B5" t="n">
-        <v>56569</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,20 +1033,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,9 +1054,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1065,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594387</v>
+        <v>594345</v>
       </c>
       <c r="R5" t="n">
-        <v>7183779</v>
+        <v>7183736</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515995</v>
+        <v>121515986</v>
       </c>
       <c r="B6" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594345</v>
+        <v>594413</v>
       </c>
       <c r="R6" t="n">
-        <v>7183736</v>
+        <v>7183672</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515996</v>
+        <v>121515988</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>82392</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594372</v>
+        <v>594414</v>
       </c>
       <c r="R7" t="n">
-        <v>7183791</v>
+        <v>7183678</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515985</v>
+        <v>121515973</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,7 +1403,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594428</v>
+        <v>594401</v>
       </c>
       <c r="R8" t="n">
-        <v>7183633</v>
+        <v>7183475</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515983</v>
+        <v>121515990</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>56570</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,30 +1496,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>102613</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1527,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594375</v>
+        <v>594387</v>
       </c>
       <c r="R9" t="n">
-        <v>7183570</v>
+        <v>7183779</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1562,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515989</v>
+        <v>121515983</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>57508</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,34 +1616,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594414</v>
+        <v>594375</v>
       </c>
       <c r="R10" t="n">
-        <v>7183679</v>
+        <v>7183570</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1674,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1689,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515982</v>
+        <v>121515984</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1756,10 +1761,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594371</v>
+        <v>594440</v>
       </c>
       <c r="R11" t="n">
-        <v>7183569</v>
+        <v>7183609</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1791,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1806,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515972</v>
+        <v>121515977</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,34 +1849,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594435</v>
+        <v>594385</v>
       </c>
       <c r="R12" t="n">
-        <v>7183446</v>
+        <v>7183550</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1903,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515986</v>
+        <v>121515994</v>
       </c>
       <c r="B13" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,39 +1966,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594413</v>
+        <v>594343</v>
       </c>
       <c r="R13" t="n">
-        <v>7183672</v>
+        <v>7183730</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2020,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,10 +2062,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515974</v>
+        <v>121515972</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2097,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594385</v>
+        <v>594435</v>
       </c>
       <c r="R14" t="n">
-        <v>7183523</v>
+        <v>7183446</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2147,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,10 +2174,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515977</v>
+        <v>121515991</v>
       </c>
       <c r="B15" t="n">
-        <v>57354</v>
+        <v>57466</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,20 +2186,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2202,10 +2207,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2214,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594385</v>
+        <v>594387</v>
       </c>
       <c r="R15" t="n">
-        <v>7183550</v>
+        <v>7183695</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2249,7 +2253,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,7 +2263,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,10 +2290,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515994</v>
+        <v>121515978</v>
       </c>
       <c r="B16" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2302,34 +2306,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594343</v>
+        <v>594389</v>
       </c>
       <c r="R16" t="n">
-        <v>7183730</v>
+        <v>7183552</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2361,7 +2370,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,7 +2380,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,10 +2407,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515980</v>
+        <v>121515987</v>
       </c>
       <c r="B17" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,34 +2423,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594371</v>
+        <v>594417</v>
       </c>
       <c r="R17" t="n">
-        <v>7183569</v>
+        <v>7183674</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2473,7 +2487,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2483,7 +2497,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2510,10 +2524,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515987</v>
+        <v>121515982</v>
       </c>
       <c r="B18" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2555,10 +2569,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594417</v>
+        <v>594371</v>
       </c>
       <c r="R18" t="n">
-        <v>7183674</v>
+        <v>7183569</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2590,7 +2604,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2600,7 +2614,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,10 +2641,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515984</v>
+        <v>121515989</v>
       </c>
       <c r="B19" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2643,39 +2657,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594440</v>
+        <v>594414</v>
       </c>
       <c r="R19" t="n">
-        <v>7183609</v>
+        <v>7183679</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2707,7 +2716,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2717,7 +2726,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,10 +2753,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515988</v>
+        <v>121515970</v>
       </c>
       <c r="B20" t="n">
-        <v>82391</v>
+        <v>82392</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2784,10 +2793,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594414</v>
+        <v>594437</v>
       </c>
       <c r="R20" t="n">
-        <v>7183678</v>
+        <v>7183445</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2819,7 +2828,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2829,7 +2838,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2856,10 +2865,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515970</v>
+        <v>121515975</v>
       </c>
       <c r="B21" t="n">
-        <v>82391</v>
+        <v>90737</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2872,21 +2881,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2896,10 +2905,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594437</v>
+        <v>594384</v>
       </c>
       <c r="R21" t="n">
-        <v>7183445</v>
+        <v>7183540</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2931,7 +2940,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2941,7 +2950,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2968,10 +2977,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515973</v>
+        <v>121515996</v>
       </c>
       <c r="B22" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2984,39 +2993,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594401</v>
+        <v>594372</v>
       </c>
       <c r="R22" t="n">
-        <v>7183475</v>
+        <v>7183791</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3048,7 +3052,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3058,7 +3062,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,10 +3089,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515976</v>
+        <v>121515985</v>
       </c>
       <c r="B23" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3101,34 +3105,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594384</v>
+        <v>594428</v>
       </c>
       <c r="R23" t="n">
-        <v>7183540</v>
+        <v>7183633</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3160,7 +3169,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3170,7 +3179,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3197,10 +3206,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515975</v>
+        <v>121515976</v>
       </c>
       <c r="B24" t="n">
-        <v>90731</v>
+        <v>78608</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3213,21 +3222,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3312,7 +3321,7 @@
         <v>121515993</v>
       </c>
       <c r="B25" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3426,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515991</v>
+        <v>121515980</v>
       </c>
       <c r="B26" t="n">
-        <v>57465</v>
+        <v>78608</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3438,42 +3447,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594387</v>
+        <v>594371</v>
       </c>
       <c r="R26" t="n">
-        <v>7183695</v>
+        <v>7183569</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3505,7 +3510,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3515,7 +3520,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,10 +3547,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515979</v>
+        <v>121515974</v>
       </c>
       <c r="B27" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3558,39 +3563,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594372</v>
+        <v>594385</v>
       </c>
       <c r="R27" t="n">
-        <v>7183568</v>
+        <v>7183523</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 30345-2024 artfynd.xlsx
+++ b/artfynd/A 30345-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515979</v>
+        <v>121515970</v>
       </c>
       <c r="B4" t="n">
-        <v>57355</v>
+        <v>82393</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594372</v>
+        <v>594437</v>
       </c>
       <c r="R4" t="n">
-        <v>7183568</v>
+        <v>7183445</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515995</v>
+        <v>121515987</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,7 +1052,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594345</v>
+        <v>594417</v>
       </c>
       <c r="R5" t="n">
-        <v>7183736</v>
+        <v>7183674</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515986</v>
+        <v>121515990</v>
       </c>
       <c r="B6" t="n">
-        <v>57355</v>
+        <v>56571</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,20 +1145,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1171,10 +1166,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1183,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594413</v>
+        <v>594387</v>
       </c>
       <c r="R6" t="n">
-        <v>7183672</v>
+        <v>7183779</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515988</v>
+        <v>121515993</v>
       </c>
       <c r="B7" t="n">
-        <v>82392</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,34 +1265,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594414</v>
+        <v>594381</v>
       </c>
       <c r="R7" t="n">
-        <v>7183678</v>
+        <v>7183690</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515973</v>
+        <v>121515996</v>
       </c>
       <c r="B8" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,39 +1382,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594401</v>
+        <v>594372</v>
       </c>
       <c r="R8" t="n">
-        <v>7183475</v>
+        <v>7183791</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1447,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515990</v>
+        <v>121515988</v>
       </c>
       <c r="B9" t="n">
-        <v>56570</v>
+        <v>82393</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,42 +1490,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102613</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594387</v>
+        <v>594414</v>
       </c>
       <c r="R9" t="n">
-        <v>7183779</v>
+        <v>7183678</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515983</v>
+        <v>121515995</v>
       </c>
       <c r="B10" t="n">
-        <v>57508</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,26 +1606,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594375</v>
+        <v>594345</v>
       </c>
       <c r="R10" t="n">
-        <v>7183570</v>
+        <v>7183736</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1679,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515984</v>
+        <v>121515975</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,39 +1723,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594440</v>
+        <v>594384</v>
       </c>
       <c r="R11" t="n">
-        <v>7183609</v>
+        <v>7183540</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1796,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515977</v>
+        <v>121515985</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,7 +1855,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1878,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594385</v>
+        <v>594428</v>
       </c>
       <c r="R12" t="n">
-        <v>7183550</v>
+        <v>7183633</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1913,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515994</v>
+        <v>121515991</v>
       </c>
       <c r="B13" t="n">
-        <v>78608</v>
+        <v>57467</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,38 +1948,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594343</v>
+        <v>594387</v>
       </c>
       <c r="R13" t="n">
-        <v>7183730</v>
+        <v>7183695</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2025,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515972</v>
+        <v>121515982</v>
       </c>
       <c r="B14" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2078,34 +2068,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594435</v>
+        <v>594371</v>
       </c>
       <c r="R14" t="n">
-        <v>7183446</v>
+        <v>7183569</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2137,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2147,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,10 +2169,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515991</v>
+        <v>121515984</v>
       </c>
       <c r="B15" t="n">
-        <v>57466</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,20 +2181,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2207,9 +2202,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2218,10 +2214,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594387</v>
+        <v>594440</v>
       </c>
       <c r="R15" t="n">
-        <v>7183695</v>
+        <v>7183609</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2253,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2263,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,10 +2286,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515978</v>
+        <v>121515972</v>
       </c>
       <c r="B16" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,39 +2302,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594389</v>
+        <v>594435</v>
       </c>
       <c r="R16" t="n">
-        <v>7183552</v>
+        <v>7183446</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2370,7 +2361,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2380,7 +2371,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,10 +2398,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515987</v>
+        <v>121515980</v>
       </c>
       <c r="B17" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,39 +2414,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594417</v>
+        <v>594371</v>
       </c>
       <c r="R17" t="n">
-        <v>7183674</v>
+        <v>7183569</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2487,7 +2473,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2497,7 +2483,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,10 +2510,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515982</v>
+        <v>121515973</v>
       </c>
       <c r="B18" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2560,7 +2546,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2569,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594371</v>
+        <v>594401</v>
       </c>
       <c r="R18" t="n">
-        <v>7183569</v>
+        <v>7183475</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2604,7 +2590,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2614,7 +2600,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2641,10 +2627,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515989</v>
+        <v>121515974</v>
       </c>
       <c r="B19" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2681,10 +2667,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594414</v>
+        <v>594385</v>
       </c>
       <c r="R19" t="n">
-        <v>7183679</v>
+        <v>7183523</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2716,7 +2702,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2726,7 +2712,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2753,10 +2739,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515970</v>
+        <v>121515989</v>
       </c>
       <c r="B20" t="n">
-        <v>82392</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2769,21 +2755,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2793,10 +2779,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594437</v>
+        <v>594414</v>
       </c>
       <c r="R20" t="n">
-        <v>7183445</v>
+        <v>7183679</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2828,7 +2814,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2838,7 +2824,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2865,10 +2851,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515975</v>
+        <v>121515994</v>
       </c>
       <c r="B21" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2881,21 +2867,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2905,10 +2891,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594384</v>
+        <v>594343</v>
       </c>
       <c r="R21" t="n">
-        <v>7183540</v>
+        <v>7183730</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2940,7 +2926,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2950,7 +2936,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2977,10 +2963,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515996</v>
+        <v>121515979</v>
       </c>
       <c r="B22" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2993,24 +2979,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -3020,7 +3011,7 @@
         <v>594372</v>
       </c>
       <c r="R22" t="n">
-        <v>7183791</v>
+        <v>7183568</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3052,7 +3043,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3062,7 +3053,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3089,10 +3080,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515985</v>
+        <v>121515983</v>
       </c>
       <c r="B23" t="n">
-        <v>57355</v>
+        <v>57509</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3105,27 +3096,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3134,10 +3124,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594428</v>
+        <v>594375</v>
       </c>
       <c r="R23" t="n">
-        <v>7183633</v>
+        <v>7183570</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3169,7 +3159,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3179,7 +3169,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,7 +3199,7 @@
         <v>121515976</v>
       </c>
       <c r="B24" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3318,10 +3308,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515993</v>
+        <v>121515978</v>
       </c>
       <c r="B25" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3354,7 +3344,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3363,10 +3353,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594381</v>
+        <v>594389</v>
       </c>
       <c r="R25" t="n">
-        <v>7183690</v>
+        <v>7183552</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3398,7 +3388,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,7 +3398,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,10 +3425,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515980</v>
+        <v>121515977</v>
       </c>
       <c r="B26" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,34 +3441,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594371</v>
+        <v>594385</v>
       </c>
       <c r="R26" t="n">
-        <v>7183569</v>
+        <v>7183550</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3510,7 +3505,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3520,7 +3515,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,10 +3542,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515974</v>
+        <v>121515986</v>
       </c>
       <c r="B27" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3563,34 +3558,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594385</v>
+        <v>594413</v>
       </c>
       <c r="R27" t="n">
-        <v>7183523</v>
+        <v>7183672</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 30345-2024 artfynd.xlsx
+++ b/artfynd/A 30345-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515970</v>
+        <v>121515972</v>
       </c>
       <c r="B4" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594437</v>
+        <v>594435</v>
       </c>
       <c r="R4" t="n">
-        <v>7183445</v>
+        <v>7183446</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515987</v>
+        <v>121515994</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594417</v>
+        <v>594343</v>
       </c>
       <c r="R5" t="n">
-        <v>7183674</v>
+        <v>7183730</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515990</v>
+        <v>121515973</v>
       </c>
       <c r="B6" t="n">
-        <v>56571</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,20 +1140,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1166,9 +1161,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1177,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594387</v>
+        <v>594401</v>
       </c>
       <c r="R6" t="n">
-        <v>7183779</v>
+        <v>7183475</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1366,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515996</v>
+        <v>121515985</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,34 +1378,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594372</v>
+        <v>594428</v>
       </c>
       <c r="R8" t="n">
-        <v>7183791</v>
+        <v>7183633</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1590,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515995</v>
+        <v>121515970</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,39 +1607,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594345</v>
+        <v>594437</v>
       </c>
       <c r="R10" t="n">
-        <v>7183736</v>
+        <v>7183445</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1670,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1819,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515985</v>
+        <v>121515989</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,39 +1831,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594428</v>
+        <v>594414</v>
       </c>
       <c r="R12" t="n">
-        <v>7183633</v>
+        <v>7183679</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1899,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515991</v>
+        <v>121515977</v>
       </c>
       <c r="B13" t="n">
-        <v>57467</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,20 +1939,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1969,9 +1960,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1980,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594387</v>
+        <v>594385</v>
       </c>
       <c r="R13" t="n">
-        <v>7183695</v>
+        <v>7183550</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2015,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515982</v>
+        <v>121515996</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,39 +2060,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594371</v>
+        <v>594372</v>
       </c>
       <c r="R14" t="n">
-        <v>7183569</v>
+        <v>7183791</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,7 +2156,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515984</v>
+        <v>121515979</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2214,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594440</v>
+        <v>594372</v>
       </c>
       <c r="R15" t="n">
-        <v>7183609</v>
+        <v>7183568</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2249,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,10 +2273,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515972</v>
+        <v>121515991</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>57467</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2298,38 +2285,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594435</v>
+        <v>594387</v>
       </c>
       <c r="R16" t="n">
-        <v>7183446</v>
+        <v>7183695</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2361,7 +2352,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,7 +2362,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515980</v>
+        <v>121515984</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,34 +2405,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594371</v>
+        <v>594440</v>
       </c>
       <c r="R17" t="n">
-        <v>7183569</v>
+        <v>7183609</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2473,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2483,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2510,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515973</v>
+        <v>121515990</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>56571</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2522,20 +2518,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2543,10 +2539,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2555,10 +2550,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594401</v>
+        <v>594387</v>
       </c>
       <c r="R18" t="n">
-        <v>7183475</v>
+        <v>7183779</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2590,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2600,7 +2595,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,10 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515974</v>
+        <v>121515982</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2643,34 +2638,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594385</v>
+        <v>594371</v>
       </c>
       <c r="R19" t="n">
-        <v>7183523</v>
+        <v>7183569</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2739,10 +2739,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515989</v>
+        <v>121515995</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2755,34 +2755,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594414</v>
+        <v>594345</v>
       </c>
       <c r="R20" t="n">
-        <v>7183679</v>
+        <v>7183736</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2814,7 +2819,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2824,7 +2829,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2851,10 +2856,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515994</v>
+        <v>121515978</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2867,34 +2872,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594343</v>
+        <v>594389</v>
       </c>
       <c r="R21" t="n">
-        <v>7183730</v>
+        <v>7183552</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2926,7 +2936,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2936,7 +2946,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,10 +2973,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515979</v>
+        <v>121515980</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2979,39 +2989,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594372</v>
+        <v>594371</v>
       </c>
       <c r="R22" t="n">
-        <v>7183568</v>
+        <v>7183569</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3080,10 +3085,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515983</v>
+        <v>121515976</v>
       </c>
       <c r="B23" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3096,38 +3101,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594375</v>
+        <v>594384</v>
       </c>
       <c r="R23" t="n">
-        <v>7183570</v>
+        <v>7183540</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3159,7 +3160,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3169,7 +3170,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,7 +3197,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515976</v>
+        <v>121515974</v>
       </c>
       <c r="B24" t="n">
         <v>78609</v>
@@ -3236,10 +3237,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594384</v>
+        <v>594385</v>
       </c>
       <c r="R24" t="n">
-        <v>7183540</v>
+        <v>7183523</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3271,7 +3272,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3281,7 +3282,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3308,7 +3309,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515978</v>
+        <v>121515986</v>
       </c>
       <c r="B25" t="n">
         <v>57356</v>
@@ -3353,10 +3354,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594389</v>
+        <v>594413</v>
       </c>
       <c r="R25" t="n">
-        <v>7183552</v>
+        <v>7183672</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3388,7 +3389,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3398,7 +3399,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3425,10 +3426,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515977</v>
+        <v>121515983</v>
       </c>
       <c r="B26" t="n">
-        <v>57356</v>
+        <v>57509</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3441,27 +3442,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594385</v>
+        <v>594375</v>
       </c>
       <c r="R26" t="n">
-        <v>7183550</v>
+        <v>7183570</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,7 +3542,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515986</v>
+        <v>121515987</v>
       </c>
       <c r="B27" t="n">
         <v>57356</v>
@@ -3578,7 +3578,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594413</v>
+        <v>594417</v>
       </c>
       <c r="R27" t="n">
-        <v>7183672</v>
+        <v>7183674</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 30345-2024 artfynd.xlsx
+++ b/artfynd/A 30345-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515972</v>
+        <v>121515978</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594435</v>
+        <v>594389</v>
       </c>
       <c r="R4" t="n">
-        <v>7183446</v>
+        <v>7183552</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515994</v>
+        <v>121515993</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594343</v>
+        <v>594381</v>
       </c>
       <c r="R5" t="n">
-        <v>7183730</v>
+        <v>7183690</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515973</v>
+        <v>121515980</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594401</v>
+        <v>594371</v>
       </c>
       <c r="R6" t="n">
-        <v>7183475</v>
+        <v>7183569</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515993</v>
+        <v>121515974</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594381</v>
+        <v>594385</v>
       </c>
       <c r="R7" t="n">
-        <v>7183690</v>
+        <v>7183523</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515985</v>
+        <v>121515994</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,39 +1378,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594428</v>
+        <v>594343</v>
       </c>
       <c r="R8" t="n">
-        <v>7183633</v>
+        <v>7183730</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515988</v>
+        <v>121515985</v>
       </c>
       <c r="B9" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,34 +1490,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594414</v>
+        <v>594428</v>
       </c>
       <c r="R9" t="n">
-        <v>7183678</v>
+        <v>7183633</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,7 +1591,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515970</v>
+        <v>121515988</v>
       </c>
       <c r="B10" t="n">
         <v>82393</v>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594437</v>
+        <v>594414</v>
       </c>
       <c r="R10" t="n">
-        <v>7183445</v>
+        <v>7183678</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515975</v>
+        <v>121515990</v>
       </c>
       <c r="B11" t="n">
-        <v>90738</v>
+        <v>56571</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,38 +1715,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>102613</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594384</v>
+        <v>594387</v>
       </c>
       <c r="R11" t="n">
-        <v>7183540</v>
+        <v>7183779</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515989</v>
+        <v>121515986</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,34 +1835,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594414</v>
+        <v>594413</v>
       </c>
       <c r="R12" t="n">
-        <v>7183679</v>
+        <v>7183672</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2044,7 +2053,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515996</v>
+        <v>121515972</v>
       </c>
       <c r="B14" t="n">
         <v>78609</v>
@@ -2084,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594372</v>
+        <v>594435</v>
       </c>
       <c r="R14" t="n">
-        <v>7183791</v>
+        <v>7183446</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,7 +2165,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515979</v>
+        <v>121515982</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2201,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594372</v>
+        <v>594371</v>
       </c>
       <c r="R15" t="n">
-        <v>7183568</v>
+        <v>7183569</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2236,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,10 +2282,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515991</v>
+        <v>121515983</v>
       </c>
       <c r="B16" t="n">
-        <v>57467</v>
+        <v>57509</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2285,30 +2294,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2317,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594387</v>
+        <v>594375</v>
       </c>
       <c r="R16" t="n">
-        <v>7183695</v>
+        <v>7183570</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2352,7 +2361,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2362,7 +2371,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,7 +2398,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515984</v>
+        <v>121515973</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2425,7 +2434,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2434,10 +2443,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594440</v>
+        <v>594401</v>
       </c>
       <c r="R17" t="n">
-        <v>7183609</v>
+        <v>7183475</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2469,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,10 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515990</v>
+        <v>121515991</v>
       </c>
       <c r="B18" t="n">
-        <v>56571</v>
+        <v>57467</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2522,16 +2531,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102613</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2541,7 +2550,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2553,7 +2562,7 @@
         <v>594387</v>
       </c>
       <c r="R18" t="n">
-        <v>7183779</v>
+        <v>7183695</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2622,7 +2631,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515982</v>
+        <v>121515995</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2658,7 +2667,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2667,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594371</v>
+        <v>594345</v>
       </c>
       <c r="R19" t="n">
-        <v>7183569</v>
+        <v>7183736</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2702,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2712,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2739,10 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515995</v>
+        <v>121515970</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2755,39 +2764,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594345</v>
+        <v>594437</v>
       </c>
       <c r="R20" t="n">
-        <v>7183736</v>
+        <v>7183445</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2819,7 +2823,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2829,7 +2833,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2856,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515978</v>
+        <v>121515996</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2872,39 +2876,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594389</v>
+        <v>594372</v>
       </c>
       <c r="R21" t="n">
-        <v>7183552</v>
+        <v>7183791</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2936,7 +2935,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2946,7 +2945,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515980</v>
+        <v>121515975</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2989,21 +2988,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3013,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594371</v>
+        <v>594384</v>
       </c>
       <c r="R22" t="n">
-        <v>7183569</v>
+        <v>7183540</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3048,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3058,7 +3057,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,10 +3084,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515976</v>
+        <v>121515979</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3101,34 +3100,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594384</v>
+        <v>594372</v>
       </c>
       <c r="R23" t="n">
-        <v>7183540</v>
+        <v>7183568</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3160,7 +3164,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3170,7 +3174,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3197,7 +3201,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515974</v>
+        <v>121515976</v>
       </c>
       <c r="B24" t="n">
         <v>78609</v>
@@ -3237,10 +3241,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594385</v>
+        <v>594384</v>
       </c>
       <c r="R24" t="n">
-        <v>7183523</v>
+        <v>7183540</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3272,7 +3276,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3282,7 +3286,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,10 +3313,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515986</v>
+        <v>121515989</v>
       </c>
       <c r="B25" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3325,39 +3329,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594413</v>
+        <v>594414</v>
       </c>
       <c r="R25" t="n">
-        <v>7183672</v>
+        <v>7183679</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3389,7 +3388,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3399,7 +3398,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3426,10 +3425,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515983</v>
+        <v>121515984</v>
       </c>
       <c r="B26" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3442,26 +3441,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594375</v>
+        <v>594440</v>
       </c>
       <c r="R26" t="n">
-        <v>7183570</v>
+        <v>7183609</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 30345-2024 artfynd.xlsx
+++ b/artfynd/A 30345-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515978</v>
+        <v>121515970</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594389</v>
+        <v>594437</v>
       </c>
       <c r="R4" t="n">
-        <v>7183552</v>
+        <v>7183445</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515993</v>
+        <v>121515985</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594381</v>
+        <v>594428</v>
       </c>
       <c r="R5" t="n">
-        <v>7183690</v>
+        <v>7183633</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515980</v>
+        <v>121515977</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594371</v>
+        <v>594385</v>
       </c>
       <c r="R6" t="n">
-        <v>7183569</v>
+        <v>7183550</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515974</v>
+        <v>121515975</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594385</v>
+        <v>594384</v>
       </c>
       <c r="R7" t="n">
-        <v>7183523</v>
+        <v>7183540</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515994</v>
+        <v>121515988</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594343</v>
+        <v>594414</v>
       </c>
       <c r="R8" t="n">
-        <v>7183730</v>
+        <v>7183678</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,7 +1474,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515985</v>
+        <v>121515982</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594428</v>
+        <v>594371</v>
       </c>
       <c r="R9" t="n">
-        <v>7183633</v>
+        <v>7183569</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515988</v>
+        <v>121515980</v>
       </c>
       <c r="B10" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594414</v>
+        <v>594371</v>
       </c>
       <c r="R10" t="n">
-        <v>7183678</v>
+        <v>7183569</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515990</v>
+        <v>121515974</v>
       </c>
       <c r="B11" t="n">
-        <v>56571</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,42 +1715,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594387</v>
+        <v>594385</v>
       </c>
       <c r="R11" t="n">
-        <v>7183779</v>
+        <v>7183523</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515986</v>
+        <v>121515976</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,39 +1831,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594413</v>
+        <v>594384</v>
       </c>
       <c r="R12" t="n">
-        <v>7183672</v>
+        <v>7183540</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1899,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,7 +1927,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515977</v>
+        <v>121515995</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1981,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594385</v>
+        <v>594345</v>
       </c>
       <c r="R13" t="n">
-        <v>7183550</v>
+        <v>7183736</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2016,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515972</v>
+        <v>121515984</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,34 +2060,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594435</v>
+        <v>594440</v>
       </c>
       <c r="R14" t="n">
-        <v>7183446</v>
+        <v>7183609</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2128,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,7 +2161,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515982</v>
+        <v>121515979</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2210,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594371</v>
+        <v>594372</v>
       </c>
       <c r="R15" t="n">
-        <v>7183569</v>
+        <v>7183568</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515983</v>
+        <v>121515990</v>
       </c>
       <c r="B16" t="n">
-        <v>57509</v>
+        <v>56571</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,30 +2290,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>102613</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2326,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594375</v>
+        <v>594387</v>
       </c>
       <c r="R16" t="n">
-        <v>7183570</v>
+        <v>7183779</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2361,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,7 +2367,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,10 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515973</v>
+        <v>121515983</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>57509</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,27 +2410,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2443,10 +2438,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594401</v>
+        <v>594375</v>
       </c>
       <c r="R17" t="n">
-        <v>7183475</v>
+        <v>7183570</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2478,7 +2473,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2483,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,10 +2510,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515991</v>
+        <v>121515986</v>
       </c>
       <c r="B18" t="n">
-        <v>57467</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,20 +2522,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2548,9 +2543,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2559,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594387</v>
+        <v>594413</v>
       </c>
       <c r="R18" t="n">
-        <v>7183695</v>
+        <v>7183672</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2594,7 +2590,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2604,7 +2600,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,7 +2627,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515995</v>
+        <v>121515993</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2667,7 +2663,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2676,10 +2672,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594345</v>
+        <v>594381</v>
       </c>
       <c r="R19" t="n">
-        <v>7183736</v>
+        <v>7183690</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2711,7 +2707,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,7 +2717,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,10 +2744,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515970</v>
+        <v>121515973</v>
       </c>
       <c r="B20" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2764,34 +2760,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594437</v>
+        <v>594401</v>
       </c>
       <c r="R20" t="n">
-        <v>7183445</v>
+        <v>7183475</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2823,7 +2824,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2833,7 +2834,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,7 +2861,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515996</v>
+        <v>121515972</v>
       </c>
       <c r="B21" t="n">
         <v>78609</v>
@@ -2900,10 +2901,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594372</v>
+        <v>594435</v>
       </c>
       <c r="R21" t="n">
-        <v>7183791</v>
+        <v>7183446</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2935,7 +2936,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2945,7 +2946,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,10 +2973,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515975</v>
+        <v>121515989</v>
       </c>
       <c r="B22" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2988,21 +2989,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3012,10 +3013,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594384</v>
+        <v>594414</v>
       </c>
       <c r="R22" t="n">
-        <v>7183540</v>
+        <v>7183679</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3047,7 +3048,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,7 +3058,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,7 +3085,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515979</v>
+        <v>121515987</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -3129,10 +3130,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594372</v>
+        <v>594417</v>
       </c>
       <c r="R23" t="n">
-        <v>7183568</v>
+        <v>7183674</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3164,7 +3165,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,7 +3175,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3201,10 +3202,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515976</v>
+        <v>121515991</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>57467</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3213,38 +3214,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594384</v>
+        <v>594387</v>
       </c>
       <c r="R24" t="n">
-        <v>7183540</v>
+        <v>7183695</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3276,7 +3281,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3286,7 +3291,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3313,7 +3318,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515989</v>
+        <v>121515994</v>
       </c>
       <c r="B25" t="n">
         <v>78609</v>
@@ -3353,10 +3358,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594414</v>
+        <v>594343</v>
       </c>
       <c r="R25" t="n">
-        <v>7183679</v>
+        <v>7183730</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3388,7 +3393,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3398,7 +3403,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3425,10 +3430,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515984</v>
+        <v>121515996</v>
       </c>
       <c r="B26" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3441,39 +3446,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594440</v>
+        <v>594372</v>
       </c>
       <c r="R26" t="n">
-        <v>7183609</v>
+        <v>7183791</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,7 +3542,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515987</v>
+        <v>121515978</v>
       </c>
       <c r="B27" t="n">
         <v>57356</v>
@@ -3578,7 +3578,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594417</v>
+        <v>594389</v>
       </c>
       <c r="R27" t="n">
-        <v>7183674</v>
+        <v>7183552</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 30345-2024 artfynd.xlsx
+++ b/artfynd/A 30345-2024 artfynd.xlsx
@@ -2278,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515990</v>
+        <v>121515983</v>
       </c>
       <c r="B16" t="n">
-        <v>56571</v>
+        <v>57509</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,30 +2290,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102613</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594387</v>
+        <v>594375</v>
       </c>
       <c r="R16" t="n">
-        <v>7183779</v>
+        <v>7183570</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,10 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515983</v>
+        <v>121515990</v>
       </c>
       <c r="B17" t="n">
-        <v>57509</v>
+        <v>56571</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2406,30 +2406,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>102613</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594375</v>
+        <v>594387</v>
       </c>
       <c r="R17" t="n">
-        <v>7183570</v>
+        <v>7183779</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 30345-2024 artfynd.xlsx
+++ b/artfynd/A 30345-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515991</v>
+        <v>121515975</v>
       </c>
       <c r="B4" t="n">
-        <v>57468</v>
+        <v>90746</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,42 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594387</v>
+        <v>594384</v>
       </c>
       <c r="R4" t="n">
-        <v>7183695</v>
+        <v>7183540</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515977</v>
+        <v>121515990</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>56572</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,20 +1028,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1053,10 +1049,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1065,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594385</v>
+        <v>594387</v>
       </c>
       <c r="R5" t="n">
-        <v>7183550</v>
+        <v>7183779</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515978</v>
+        <v>121515988</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,39 +1148,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594389</v>
+        <v>594414</v>
       </c>
       <c r="R6" t="n">
-        <v>7183552</v>
+        <v>7183678</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515989</v>
+        <v>121515970</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594414</v>
+        <v>594437</v>
       </c>
       <c r="R7" t="n">
-        <v>7183679</v>
+        <v>7183445</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,7 +1356,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515982</v>
+        <v>121515977</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1402,7 +1392,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594371</v>
+        <v>594385</v>
       </c>
       <c r="R8" t="n">
-        <v>7183569</v>
+        <v>7183550</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515990</v>
+        <v>121515985</v>
       </c>
       <c r="B9" t="n">
-        <v>56572</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,20 +1485,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1516,9 +1506,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1527,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594387</v>
+        <v>594428</v>
       </c>
       <c r="R9" t="n">
-        <v>7183779</v>
+        <v>7183633</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1562,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,7 +1590,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515993</v>
+        <v>121515984</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1644,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594381</v>
+        <v>594440</v>
       </c>
       <c r="R10" t="n">
-        <v>7183690</v>
+        <v>7183609</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1679,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515988</v>
+        <v>121515996</v>
       </c>
       <c r="B11" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,21 +1723,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1756,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594414</v>
+        <v>594372</v>
       </c>
       <c r="R11" t="n">
-        <v>7183678</v>
+        <v>7183791</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1791,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515970</v>
+        <v>121515987</v>
       </c>
       <c r="B12" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,34 +1835,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594437</v>
+        <v>594417</v>
       </c>
       <c r="R12" t="n">
-        <v>7183445</v>
+        <v>7183674</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1903,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2052,10 +2048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515972</v>
+        <v>121515995</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,34 +2064,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594435</v>
+        <v>594345</v>
       </c>
       <c r="R14" t="n">
-        <v>7183446</v>
+        <v>7183736</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2127,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515984</v>
+        <v>121515976</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,39 +2181,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594440</v>
+        <v>594384</v>
       </c>
       <c r="R15" t="n">
-        <v>7183609</v>
+        <v>7183540</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2250,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,10 +2277,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515985</v>
+        <v>121515972</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,39 +2293,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594428</v>
+        <v>594435</v>
       </c>
       <c r="R16" t="n">
-        <v>7183633</v>
+        <v>7183446</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2361,7 +2352,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,7 +2362,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515983</v>
+        <v>121515993</v>
       </c>
       <c r="B17" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,26 +2405,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2442,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594375</v>
+        <v>594381</v>
       </c>
       <c r="R17" t="n">
-        <v>7183570</v>
+        <v>7183690</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2477,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,7 +2506,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515995</v>
+        <v>121515986</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2559,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594345</v>
+        <v>594413</v>
       </c>
       <c r="R18" t="n">
-        <v>7183736</v>
+        <v>7183672</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2594,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2604,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,7 +2623,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515994</v>
+        <v>121515989</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2671,10 +2663,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594343</v>
+        <v>594414</v>
       </c>
       <c r="R19" t="n">
-        <v>7183730</v>
+        <v>7183679</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2706,7 +2698,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,7 +2708,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,10 +2735,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515986</v>
+        <v>121515983</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2759,27 +2751,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2788,10 +2779,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594413</v>
+        <v>594375</v>
       </c>
       <c r="R20" t="n">
-        <v>7183672</v>
+        <v>7183570</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2823,7 +2814,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2833,7 +2824,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,7 +2851,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515973</v>
+        <v>121515978</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2905,10 +2896,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594401</v>
+        <v>594389</v>
       </c>
       <c r="R21" t="n">
-        <v>7183475</v>
+        <v>7183552</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2940,7 +2931,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2950,7 +2941,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2977,10 +2968,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515976</v>
+        <v>121515991</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
+        <v>57468</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2989,38 +2980,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594384</v>
+        <v>594387</v>
       </c>
       <c r="R22" t="n">
-        <v>7183540</v>
+        <v>7183695</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3052,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3062,7 +3057,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3089,10 +3084,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515980</v>
+        <v>121515982</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3105,24 +3100,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3201,7 +3201,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515979</v>
+        <v>121515973</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3237,7 +3237,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594372</v>
+        <v>594401</v>
       </c>
       <c r="R24" t="n">
-        <v>7183568</v>
+        <v>7183475</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515996</v>
+        <v>121515979</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3334,24 +3334,29 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -3361,7 +3366,7 @@
         <v>594372</v>
       </c>
       <c r="R25" t="n">
-        <v>7183791</v>
+        <v>7183568</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3393,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3403,7 +3408,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3430,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515987</v>
+        <v>121515994</v>
       </c>
       <c r="B26" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3446,39 +3451,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594417</v>
+        <v>594343</v>
       </c>
       <c r="R26" t="n">
-        <v>7183674</v>
+        <v>7183730</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,10 +3547,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515975</v>
+        <v>121515980</v>
       </c>
       <c r="B27" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3563,21 +3563,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594384</v>
+        <v>594371</v>
       </c>
       <c r="R27" t="n">
-        <v>7183540</v>
+        <v>7183569</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 30345-2024 artfynd.xlsx
+++ b/artfynd/A 30345-2024 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515983</v>
+        <v>121515978</v>
       </c>
       <c r="B20" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2751,26 +2751,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2779,10 +2780,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594375</v>
+        <v>594389</v>
       </c>
       <c r="R20" t="n">
-        <v>7183570</v>
+        <v>7183552</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2814,7 +2815,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2824,7 +2825,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2851,10 +2852,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515978</v>
+        <v>121515983</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2867,27 +2868,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594389</v>
+        <v>594375</v>
       </c>
       <c r="R21" t="n">
-        <v>7183552</v>
+        <v>7183570</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515979</v>
+        <v>121515994</v>
       </c>
       <c r="B25" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3334,39 +3334,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594372</v>
+        <v>594343</v>
       </c>
       <c r="R25" t="n">
-        <v>7183568</v>
+        <v>7183730</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3398,7 +3393,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,7 +3403,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,10 +3430,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515994</v>
+        <v>121515979</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,34 +3446,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594343</v>
+        <v>594372</v>
       </c>
       <c r="R26" t="n">
-        <v>7183730</v>
+        <v>7183568</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 30345-2024 artfynd.xlsx
+++ b/artfynd/A 30345-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515975</v>
+        <v>121515972</v>
       </c>
       <c r="B4" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594384</v>
+        <v>594435</v>
       </c>
       <c r="R4" t="n">
-        <v>7183540</v>
+        <v>7183446</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515990</v>
+        <v>121515970</v>
       </c>
       <c r="B5" t="n">
-        <v>56572</v>
+        <v>82400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,42 +1028,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594387</v>
+        <v>594437</v>
       </c>
       <c r="R5" t="n">
-        <v>7183779</v>
+        <v>7183445</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515988</v>
+        <v>121515977</v>
       </c>
       <c r="B6" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594414</v>
+        <v>594385</v>
       </c>
       <c r="R6" t="n">
-        <v>7183678</v>
+        <v>7183550</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1207,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515970</v>
+        <v>121515985</v>
       </c>
       <c r="B7" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,34 +1261,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594437</v>
+        <v>594428</v>
       </c>
       <c r="R7" t="n">
-        <v>7183445</v>
+        <v>7183633</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515977</v>
+        <v>121515991</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>57468</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,20 +1374,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1389,10 +1395,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1401,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594385</v>
+        <v>594387</v>
       </c>
       <c r="R8" t="n">
-        <v>7183550</v>
+        <v>7183695</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,7 +1478,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515985</v>
+        <v>121515982</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1518,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594428</v>
+        <v>594371</v>
       </c>
       <c r="R9" t="n">
-        <v>7183633</v>
+        <v>7183569</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1553,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515984</v>
+        <v>121515973</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1626,7 +1631,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1635,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594440</v>
+        <v>594401</v>
       </c>
       <c r="R10" t="n">
-        <v>7183609</v>
+        <v>7183475</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1670,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515996</v>
+        <v>121515975</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,21 +1728,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1747,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594372</v>
+        <v>594384</v>
       </c>
       <c r="R11" t="n">
-        <v>7183791</v>
+        <v>7183540</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,7 +1824,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515987</v>
+        <v>121515978</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1855,7 +1860,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1864,10 +1869,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594417</v>
+        <v>594389</v>
       </c>
       <c r="R12" t="n">
-        <v>7183674</v>
+        <v>7183552</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1899,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515974</v>
+        <v>121515988</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,21 +1957,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1976,10 +1981,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594385</v>
+        <v>594414</v>
       </c>
       <c r="R13" t="n">
-        <v>7183523</v>
+        <v>7183678</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2011,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,7 +2053,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515995</v>
+        <v>121515984</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2084,7 +2089,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2093,10 +2098,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594345</v>
+        <v>594440</v>
       </c>
       <c r="R14" t="n">
-        <v>7183736</v>
+        <v>7183609</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2128,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515976</v>
+        <v>121515990</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>56572</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,38 +2182,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594384</v>
+        <v>594387</v>
       </c>
       <c r="R15" t="n">
-        <v>7183540</v>
+        <v>7183779</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2240,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,10 +2286,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515972</v>
+        <v>121515983</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,34 +2302,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594435</v>
+        <v>594375</v>
       </c>
       <c r="R16" t="n">
-        <v>7183446</v>
+        <v>7183570</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2352,7 +2365,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2362,7 +2375,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,10 +2402,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515993</v>
+        <v>121515976</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,39 +2418,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594381</v>
+        <v>594384</v>
       </c>
       <c r="R17" t="n">
-        <v>7183690</v>
+        <v>7183540</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2469,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,10 +2514,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515986</v>
+        <v>121515980</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2522,39 +2530,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594413</v>
+        <v>594371</v>
       </c>
       <c r="R18" t="n">
-        <v>7183672</v>
+        <v>7183569</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2586,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2735,7 +2738,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515978</v>
+        <v>121515987</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2771,7 +2774,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2780,10 +2783,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594389</v>
+        <v>594417</v>
       </c>
       <c r="R20" t="n">
-        <v>7183552</v>
+        <v>7183674</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2815,7 +2818,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2825,7 +2828,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,10 +2855,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515983</v>
+        <v>121515994</v>
       </c>
       <c r="B21" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2868,38 +2871,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594375</v>
+        <v>594343</v>
       </c>
       <c r="R21" t="n">
-        <v>7183570</v>
+        <v>7183730</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2931,7 +2930,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2941,7 +2940,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2968,10 +2967,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515991</v>
+        <v>121515993</v>
       </c>
       <c r="B22" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2980,20 +2979,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3001,9 +3000,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594387</v>
+        <v>594381</v>
       </c>
       <c r="R22" t="n">
-        <v>7183695</v>
+        <v>7183690</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,7 +3084,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515982</v>
+        <v>121515979</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594371</v>
+        <v>594372</v>
       </c>
       <c r="R23" t="n">
-        <v>7183569</v>
+        <v>7183568</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3201,10 +3201,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515973</v>
+        <v>121515974</v>
       </c>
       <c r="B24" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3217,39 +3217,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594401</v>
+        <v>594385</v>
       </c>
       <c r="R24" t="n">
-        <v>7183475</v>
+        <v>7183523</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3281,7 +3276,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3291,7 +3286,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3318,7 +3313,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515994</v>
+        <v>121515996</v>
       </c>
       <c r="B25" t="n">
         <v>78616</v>
@@ -3358,10 +3353,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594343</v>
+        <v>594372</v>
       </c>
       <c r="R25" t="n">
-        <v>7183730</v>
+        <v>7183791</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3393,7 +3388,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3403,7 +3398,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3430,7 +3425,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515979</v>
+        <v>121515986</v>
       </c>
       <c r="B26" t="n">
         <v>57357</v>
@@ -3466,7 +3461,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3475,10 +3470,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594372</v>
+        <v>594413</v>
       </c>
       <c r="R26" t="n">
-        <v>7183568</v>
+        <v>7183672</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3510,7 +3505,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3520,7 +3515,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,10 +3542,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515980</v>
+        <v>121515995</v>
       </c>
       <c r="B27" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3563,34 +3558,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594371</v>
+        <v>594345</v>
       </c>
       <c r="R27" t="n">
-        <v>7183569</v>
+        <v>7183736</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 30345-2024 artfynd.xlsx
+++ b/artfynd/A 30345-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515972</v>
+        <v>121515996</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594435</v>
+        <v>594372</v>
       </c>
       <c r="R4" t="n">
-        <v>7183446</v>
+        <v>7183791</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515970</v>
+        <v>121515983</v>
       </c>
       <c r="B5" t="n">
-        <v>82400</v>
+        <v>57510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594437</v>
+        <v>594375</v>
       </c>
       <c r="R5" t="n">
-        <v>7183445</v>
+        <v>7183570</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515977</v>
+        <v>121515985</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1164,7 +1168,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1173,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594385</v>
+        <v>594428</v>
       </c>
       <c r="R6" t="n">
-        <v>7183550</v>
+        <v>7183633</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515985</v>
+        <v>121515974</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1265,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594428</v>
+        <v>594385</v>
       </c>
       <c r="R7" t="n">
-        <v>7183633</v>
+        <v>7183523</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515991</v>
+        <v>121515986</v>
       </c>
       <c r="B8" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,20 +1373,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1395,9 +1394,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594387</v>
+        <v>594413</v>
       </c>
       <c r="R8" t="n">
-        <v>7183695</v>
+        <v>7183672</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515982</v>
+        <v>121515991</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>57468</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,20 +1490,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1511,10 +1511,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1523,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594371</v>
+        <v>594387</v>
       </c>
       <c r="R9" t="n">
-        <v>7183569</v>
+        <v>7183695</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1558,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515973</v>
+        <v>121515975</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,39 +1610,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594401</v>
+        <v>594384</v>
       </c>
       <c r="R10" t="n">
-        <v>7183475</v>
+        <v>7183540</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1675,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515975</v>
+        <v>121515972</v>
       </c>
       <c r="B11" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,21 +1722,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1752,10 +1746,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594384</v>
+        <v>594435</v>
       </c>
       <c r="R11" t="n">
-        <v>7183540</v>
+        <v>7183446</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1787,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,7 +1818,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515978</v>
+        <v>121515973</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1869,10 +1863,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594389</v>
+        <v>594401</v>
       </c>
       <c r="R12" t="n">
-        <v>7183552</v>
+        <v>7183475</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1904,7 +1898,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1908,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515988</v>
+        <v>121515979</v>
       </c>
       <c r="B13" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,34 +1951,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594414</v>
+        <v>594372</v>
       </c>
       <c r="R13" t="n">
-        <v>7183678</v>
+        <v>7183568</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2016,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515984</v>
+        <v>121515988</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,39 +2068,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594440</v>
+        <v>594414</v>
       </c>
       <c r="R14" t="n">
-        <v>7183609</v>
+        <v>7183678</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2133,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515990</v>
+        <v>121515982</v>
       </c>
       <c r="B15" t="n">
-        <v>56572</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,20 +2176,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2203,9 +2197,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2214,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594387</v>
+        <v>594371</v>
       </c>
       <c r="R15" t="n">
-        <v>7183779</v>
+        <v>7183569</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2249,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,10 +2281,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515983</v>
+        <v>121515995</v>
       </c>
       <c r="B16" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2302,26 +2297,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2330,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594375</v>
+        <v>594345</v>
       </c>
       <c r="R16" t="n">
-        <v>7183570</v>
+        <v>7183736</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2365,7 +2361,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2375,7 +2371,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,10 +2398,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515976</v>
+        <v>121515978</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,34 +2414,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594384</v>
+        <v>594389</v>
       </c>
       <c r="R17" t="n">
-        <v>7183540</v>
+        <v>7183552</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2477,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,10 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515980</v>
+        <v>121515977</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2530,34 +2531,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594371</v>
+        <v>594385</v>
       </c>
       <c r="R18" t="n">
-        <v>7183569</v>
+        <v>7183550</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2589,7 +2595,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2605,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,7 +2632,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515989</v>
+        <v>121515994</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2666,10 +2672,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594414</v>
+        <v>594343</v>
       </c>
       <c r="R19" t="n">
-        <v>7183679</v>
+        <v>7183730</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2701,7 +2707,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,7 +2717,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,7 +2744,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515987</v>
+        <v>121515984</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2783,10 +2789,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594417</v>
+        <v>594440</v>
       </c>
       <c r="R20" t="n">
-        <v>7183674</v>
+        <v>7183609</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2818,7 +2824,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2828,7 +2834,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2855,10 +2861,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515994</v>
+        <v>121515970</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2871,21 +2877,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2895,10 +2901,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594343</v>
+        <v>594437</v>
       </c>
       <c r="R21" t="n">
-        <v>7183730</v>
+        <v>7183445</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2930,7 +2936,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2940,7 +2946,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2967,10 +2973,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515993</v>
+        <v>121515990</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
+        <v>56572</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2979,20 +2985,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3000,10 +3006,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3012,10 +3017,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594381</v>
+        <v>594387</v>
       </c>
       <c r="R22" t="n">
-        <v>7183690</v>
+        <v>7183779</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3047,7 +3052,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,7 +3062,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,7 +3089,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515979</v>
+        <v>121515993</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -3129,10 +3134,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594372</v>
+        <v>594381</v>
       </c>
       <c r="R23" t="n">
-        <v>7183568</v>
+        <v>7183690</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3164,7 +3169,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,7 +3179,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3201,7 +3206,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515974</v>
+        <v>121515989</v>
       </c>
       <c r="B24" t="n">
         <v>78616</v>
@@ -3241,10 +3246,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594385</v>
+        <v>594414</v>
       </c>
       <c r="R24" t="n">
-        <v>7183523</v>
+        <v>7183679</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3276,7 +3281,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3286,7 +3291,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3313,7 +3318,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515996</v>
+        <v>121515980</v>
       </c>
       <c r="B25" t="n">
         <v>78616</v>
@@ -3353,10 +3358,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594372</v>
+        <v>594371</v>
       </c>
       <c r="R25" t="n">
-        <v>7183791</v>
+        <v>7183569</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3388,7 +3393,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3398,7 +3403,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3425,10 +3430,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515986</v>
+        <v>121515976</v>
       </c>
       <c r="B26" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3441,39 +3446,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594413</v>
+        <v>594384</v>
       </c>
       <c r="R26" t="n">
-        <v>7183672</v>
+        <v>7183540</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,7 +3542,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515995</v>
+        <v>121515987</v>
       </c>
       <c r="B27" t="n">
         <v>57357</v>
@@ -3578,7 +3578,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594345</v>
+        <v>594417</v>
       </c>
       <c r="R27" t="n">
-        <v>7183736</v>
+        <v>7183674</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 30345-2024 artfynd.xlsx
+++ b/artfynd/A 30345-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515996</v>
+        <v>121515982</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594372</v>
+        <v>594371</v>
       </c>
       <c r="R4" t="n">
-        <v>7183791</v>
+        <v>7183569</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515983</v>
+        <v>121515990</v>
       </c>
       <c r="B5" t="n">
-        <v>57510</v>
+        <v>56572</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,30 +1033,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594375</v>
+        <v>594387</v>
       </c>
       <c r="R5" t="n">
-        <v>7183570</v>
+        <v>7183779</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515985</v>
+        <v>121515989</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,39 +1153,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594428</v>
+        <v>594414</v>
       </c>
       <c r="R6" t="n">
-        <v>7183633</v>
+        <v>7183679</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515974</v>
+        <v>121515995</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,34 +1265,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594385</v>
+        <v>594345</v>
       </c>
       <c r="R7" t="n">
-        <v>7183523</v>
+        <v>7183736</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1478,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515991</v>
+        <v>121515996</v>
       </c>
       <c r="B9" t="n">
-        <v>57468</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,42 +1495,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594387</v>
+        <v>594372</v>
       </c>
       <c r="R9" t="n">
-        <v>7183695</v>
+        <v>7183791</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1557,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515975</v>
+        <v>121515977</v>
       </c>
       <c r="B10" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,34 +1611,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594384</v>
+        <v>594385</v>
       </c>
       <c r="R10" t="n">
-        <v>7183540</v>
+        <v>7183550</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515972</v>
+        <v>121515991</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>57468</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,38 +1724,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594435</v>
+        <v>594387</v>
       </c>
       <c r="R11" t="n">
-        <v>7183446</v>
+        <v>7183695</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1781,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,7 +1828,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515973</v>
+        <v>121515978</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1863,10 +1873,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594401</v>
+        <v>594389</v>
       </c>
       <c r="R12" t="n">
-        <v>7183475</v>
+        <v>7183552</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1898,7 +1908,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1908,7 +1918,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,10 +1945,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515979</v>
+        <v>121515988</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,39 +1961,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594372</v>
+        <v>594414</v>
       </c>
       <c r="R13" t="n">
-        <v>7183568</v>
+        <v>7183678</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2015,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2030,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515988</v>
+        <v>121515984</v>
       </c>
       <c r="B14" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,34 +2073,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594414</v>
+        <v>594440</v>
       </c>
       <c r="R14" t="n">
-        <v>7183678</v>
+        <v>7183609</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2127,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2147,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,7 +2174,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515982</v>
+        <v>121515973</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2200,7 +2210,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2209,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594371</v>
+        <v>594401</v>
       </c>
       <c r="R15" t="n">
-        <v>7183569</v>
+        <v>7183475</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515995</v>
+        <v>121515970</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,39 +2307,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594345</v>
+        <v>594437</v>
       </c>
       <c r="R16" t="n">
-        <v>7183736</v>
+        <v>7183445</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2361,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,7 +2376,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515978</v>
+        <v>121515972</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,39 +2419,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594389</v>
+        <v>594435</v>
       </c>
       <c r="R17" t="n">
-        <v>7183552</v>
+        <v>7183446</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,7 +2515,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515977</v>
+        <v>121515985</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2551,7 +2551,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594385</v>
+        <v>594428</v>
       </c>
       <c r="R18" t="n">
-        <v>7183550</v>
+        <v>7183633</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,7 +2632,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515994</v>
+        <v>121515980</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594343</v>
+        <v>594371</v>
       </c>
       <c r="R19" t="n">
-        <v>7183730</v>
+        <v>7183569</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,10 +2744,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515984</v>
+        <v>121515976</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2760,39 +2760,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594440</v>
+        <v>594384</v>
       </c>
       <c r="R20" t="n">
-        <v>7183609</v>
+        <v>7183540</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2824,7 +2819,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2834,7 +2829,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,10 +2856,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515970</v>
+        <v>121515983</v>
       </c>
       <c r="B21" t="n">
-        <v>82400</v>
+        <v>57510</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2877,34 +2872,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594437</v>
+        <v>594375</v>
       </c>
       <c r="R21" t="n">
-        <v>7183445</v>
+        <v>7183570</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2936,7 +2935,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2946,7 +2945,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515990</v>
+        <v>121515974</v>
       </c>
       <c r="B22" t="n">
-        <v>56572</v>
+        <v>78616</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2985,42 +2984,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594387</v>
+        <v>594385</v>
       </c>
       <c r="R22" t="n">
-        <v>7183779</v>
+        <v>7183523</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3052,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3062,7 +3057,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3206,10 +3201,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515989</v>
+        <v>121515979</v>
       </c>
       <c r="B24" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3222,34 +3217,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594414</v>
+        <v>594372</v>
       </c>
       <c r="R24" t="n">
-        <v>7183679</v>
+        <v>7183568</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515980</v>
+        <v>121515975</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3334,21 +3334,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594371</v>
+        <v>594384</v>
       </c>
       <c r="R25" t="n">
-        <v>7183569</v>
+        <v>7183540</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3430,10 +3430,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515976</v>
+        <v>121515987</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3446,34 +3446,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594384</v>
+        <v>594417</v>
       </c>
       <c r="R26" t="n">
-        <v>7183540</v>
+        <v>7183674</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3505,7 +3510,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3515,7 +3520,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,10 +3547,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515987</v>
+        <v>121515994</v>
       </c>
       <c r="B27" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3558,39 +3563,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594417</v>
+        <v>594343</v>
       </c>
       <c r="R27" t="n">
-        <v>7183674</v>
+        <v>7183730</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 30345-2024 artfynd.xlsx
+++ b/artfynd/A 30345-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515982</v>
+        <v>121515979</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594371</v>
+        <v>594372</v>
       </c>
       <c r="R4" t="n">
-        <v>7183569</v>
+        <v>7183568</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515990</v>
+        <v>121515973</v>
       </c>
       <c r="B5" t="n">
-        <v>56572</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,20 +1033,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,9 +1054,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1065,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594387</v>
+        <v>594401</v>
       </c>
       <c r="R5" t="n">
-        <v>7183779</v>
+        <v>7183475</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515989</v>
+        <v>121515983</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,34 +1154,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594414</v>
+        <v>594375</v>
       </c>
       <c r="R6" t="n">
-        <v>7183679</v>
+        <v>7183570</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1366,7 +1371,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515986</v>
+        <v>121515982</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1402,7 +1407,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594413</v>
+        <v>594371</v>
       </c>
       <c r="R8" t="n">
-        <v>7183672</v>
+        <v>7183569</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515996</v>
+        <v>121515970</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,21 +1504,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594372</v>
+        <v>594437</v>
       </c>
       <c r="R9" t="n">
-        <v>7183791</v>
+        <v>7183445</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1558,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515977</v>
+        <v>121515987</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1631,7 +1636,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1640,10 +1645,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594385</v>
+        <v>594417</v>
       </c>
       <c r="R10" t="n">
-        <v>7183550</v>
+        <v>7183674</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1675,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515991</v>
+        <v>121515986</v>
       </c>
       <c r="B11" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,20 +1729,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1745,9 +1750,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1756,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594387</v>
+        <v>594413</v>
       </c>
       <c r="R11" t="n">
-        <v>7183695</v>
+        <v>7183672</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1791,7 +1797,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1807,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,10 +1834,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515978</v>
+        <v>121515975</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,39 +1850,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594389</v>
+        <v>594384</v>
       </c>
       <c r="R12" t="n">
-        <v>7183552</v>
+        <v>7183540</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1908,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1918,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2057,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515984</v>
+        <v>121515972</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2073,39 +2074,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594440</v>
+        <v>594435</v>
       </c>
       <c r="R14" t="n">
-        <v>7183609</v>
+        <v>7183446</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2137,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2147,7 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515973</v>
+        <v>121515974</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2190,39 +2186,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594401</v>
+        <v>594385</v>
       </c>
       <c r="R15" t="n">
-        <v>7183475</v>
+        <v>7183523</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2254,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2282,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515970</v>
+        <v>121515978</v>
       </c>
       <c r="B16" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,34 +2298,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594437</v>
+        <v>594389</v>
       </c>
       <c r="R16" t="n">
-        <v>7183445</v>
+        <v>7183552</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2366,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,7 +2399,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515972</v>
+        <v>121515980</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2443,10 +2439,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594435</v>
+        <v>594371</v>
       </c>
       <c r="R17" t="n">
-        <v>7183446</v>
+        <v>7183569</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2478,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2484,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2632,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515980</v>
+        <v>121515984</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2648,34 +2644,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594371</v>
+        <v>594440</v>
       </c>
       <c r="R19" t="n">
-        <v>7183569</v>
+        <v>7183609</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2707,7 +2708,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2717,7 +2718,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515976</v>
+        <v>121515991</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>57468</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2756,38 +2757,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594384</v>
+        <v>594387</v>
       </c>
       <c r="R20" t="n">
-        <v>7183540</v>
+        <v>7183695</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2819,7 +2824,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2829,7 +2834,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2856,10 +2861,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515983</v>
+        <v>121515976</v>
       </c>
       <c r="B21" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2872,38 +2877,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594375</v>
+        <v>594384</v>
       </c>
       <c r="R21" t="n">
-        <v>7183570</v>
+        <v>7183540</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2935,7 +2936,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2945,7 +2946,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,7 +2973,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515974</v>
+        <v>121515994</v>
       </c>
       <c r="B22" t="n">
         <v>78616</v>
@@ -3012,10 +3013,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594385</v>
+        <v>594343</v>
       </c>
       <c r="R22" t="n">
-        <v>7183523</v>
+        <v>7183730</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3047,7 +3048,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,7 +3058,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,10 +3085,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515993</v>
+        <v>121515996</v>
       </c>
       <c r="B23" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3100,39 +3101,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594381</v>
+        <v>594372</v>
       </c>
       <c r="R23" t="n">
-        <v>7183690</v>
+        <v>7183791</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3164,7 +3160,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,7 +3170,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3201,10 +3197,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515979</v>
+        <v>121515990</v>
       </c>
       <c r="B24" t="n">
-        <v>57357</v>
+        <v>56572</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3213,20 +3209,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3234,10 +3230,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3246,10 +3241,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594372</v>
+        <v>594387</v>
       </c>
       <c r="R24" t="n">
-        <v>7183568</v>
+        <v>7183779</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3281,7 +3276,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3291,7 +3286,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3318,10 +3313,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515975</v>
+        <v>121515989</v>
       </c>
       <c r="B25" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3334,21 +3329,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3358,10 +3353,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594384</v>
+        <v>594414</v>
       </c>
       <c r="R25" t="n">
-        <v>7183540</v>
+        <v>7183679</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3393,7 +3388,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3403,7 +3398,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3430,7 +3425,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515987</v>
+        <v>121515993</v>
       </c>
       <c r="B26" t="n">
         <v>57357</v>
@@ -3475,10 +3470,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594417</v>
+        <v>594381</v>
       </c>
       <c r="R26" t="n">
-        <v>7183674</v>
+        <v>7183690</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3510,7 +3505,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3520,7 +3515,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,10 +3542,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515994</v>
+        <v>121515977</v>
       </c>
       <c r="B27" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3563,34 +3558,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594343</v>
+        <v>594385</v>
       </c>
       <c r="R27" t="n">
-        <v>7183730</v>
+        <v>7183550</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 30345-2024 artfynd.xlsx
+++ b/artfynd/A 30345-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80554801</v>
+        <v>121515970</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norra sverige, Ås lm</t>
+          <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594327.7946430545</v>
+        <v>594437</v>
       </c>
       <c r="R2" t="n">
-        <v>7183738.193463838</v>
+        <v>7183445</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Endast hackspår</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,65 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80557213</v>
+        <v>121515988</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norra Sverige, Ås lm</t>
+          <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594362.9920740792</v>
+        <v>594414</v>
       </c>
       <c r="R3" t="n">
-        <v>7183529.171815267</v>
+        <v>7183678</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,67 +877,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515979</v>
+        <v>121515972</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594372</v>
+        <v>594435</v>
       </c>
       <c r="R4" t="n">
-        <v>7183568</v>
+        <v>7183446</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,55 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515973</v>
+        <v>121515974</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594401</v>
+        <v>594385</v>
       </c>
       <c r="R5" t="n">
-        <v>7183475</v>
+        <v>7183523</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,54 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515983</v>
+        <v>121515976</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594375</v>
+        <v>594384</v>
       </c>
       <c r="R6" t="n">
-        <v>7183570</v>
+        <v>7183540</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,55 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515995</v>
+        <v>121515980</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594345</v>
+        <v>594371</v>
       </c>
       <c r="R7" t="n">
-        <v>7183736</v>
+        <v>7183569</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1334,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,55 +1317,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515982</v>
+        <v>121515989</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594371</v>
+        <v>594414</v>
       </c>
       <c r="R8" t="n">
-        <v>7183569</v>
+        <v>7183678</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1451,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,37 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515970</v>
+        <v>121515994</v>
       </c>
       <c r="B9" t="n">
-        <v>82400</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1528,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594437</v>
+        <v>594343</v>
       </c>
       <c r="R9" t="n">
-        <v>7183445</v>
+        <v>7183730</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,55 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515987</v>
+        <v>121515996</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594417</v>
+        <v>594372</v>
       </c>
       <c r="R10" t="n">
-        <v>7183674</v>
+        <v>7183791</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1680,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,58 +1638,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515986</v>
+        <v>80557213</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bullersjön, Ås lm</t>
+          <t>Norra Sverige, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594413</v>
+        <v>594363</v>
       </c>
       <c r="R11" t="n">
-        <v>7183672</v>
+        <v>7183529</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1792,22 +1703,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2019-08-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2019-08-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,27 +1733,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515975</v>
+        <v>80554801</v>
       </c>
       <c r="B12" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,37 +1756,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bullersjön, Ås lm</t>
+          <t>Norra sverige, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594384</v>
+        <v>594328</v>
       </c>
       <c r="R12" t="n">
-        <v>7183540</v>
+        <v>7183738</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,22 +1810,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2019-08-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2019-08-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Endast hackspår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,27 +1845,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515988</v>
+        <v>121515973</v>
       </c>
       <c r="B13" t="n">
-        <v>82400</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,34 +1868,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594414</v>
+        <v>594401</v>
       </c>
       <c r="R13" t="n">
-        <v>7183678</v>
+        <v>7183475</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2021,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,15 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515972</v>
+        <v>121515977</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,34 +1980,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594435</v>
+        <v>594385</v>
       </c>
       <c r="R14" t="n">
-        <v>7183446</v>
+        <v>7183550</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2133,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,15 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515974</v>
+        <v>121515978</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,34 +2092,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594385</v>
+        <v>594389</v>
       </c>
       <c r="R15" t="n">
-        <v>7183523</v>
+        <v>7183552</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,15 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515978</v>
+        <v>121515979</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2224,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2327,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594389</v>
+        <v>594372</v>
       </c>
       <c r="R16" t="n">
-        <v>7183552</v>
+        <v>7183568</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2362,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2278,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,15 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515980</v>
+        <v>121515982</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,24 +2316,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -2474,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,15 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515985</v>
+        <v>121515984</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594428</v>
+        <v>594440</v>
       </c>
       <c r="R18" t="n">
-        <v>7183633</v>
+        <v>7183609</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2591,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,7 +2502,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,15 +2529,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515984</v>
+        <v>121515985</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2673,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594440</v>
+        <v>594428</v>
       </c>
       <c r="R19" t="n">
-        <v>7183609</v>
+        <v>7183633</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2708,7 +2604,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,7 +2614,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,32 +2641,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515991</v>
+        <v>121515986</v>
       </c>
       <c r="B20" t="n">
-        <v>57468</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2778,9 +2669,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2789,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594387</v>
+        <v>594413</v>
       </c>
       <c r="R20" t="n">
-        <v>7183695</v>
+        <v>7183672</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2824,7 +2716,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2834,7 +2726,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,15 +2753,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515976</v>
+        <v>121515987</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2877,34 +2764,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594384</v>
+        <v>594417</v>
       </c>
       <c r="R21" t="n">
-        <v>7183540</v>
+        <v>7183674</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2936,7 +2828,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2946,7 +2838,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,15 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515994</v>
+        <v>121515993</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,34 +2876,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594343</v>
+        <v>594381</v>
       </c>
       <c r="R22" t="n">
-        <v>7183730</v>
+        <v>7183690</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3048,7 +2940,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3058,7 +2950,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,15 +2977,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515996</v>
+        <v>121515995</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3101,34 +2988,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594372</v>
+        <v>594345</v>
       </c>
       <c r="R23" t="n">
-        <v>7183791</v>
+        <v>7183736</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3160,7 +3052,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3170,7 +3062,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3200,12 +3092,7 @@
         <v>121515990</v>
       </c>
       <c r="B24" t="n">
-        <v>56572</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3313,15 +3200,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515989</v>
+        <v>121515983</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3329,34 +3211,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594414</v>
+        <v>594375</v>
       </c>
       <c r="R25" t="n">
-        <v>7183679</v>
+        <v>7183570</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3388,7 +3274,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3398,7 +3284,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3425,15 +3311,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515993</v>
+        <v>121515991</v>
       </c>
       <c r="B26" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3441,16 +3322,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3458,10 +3339,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3470,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594381</v>
+        <v>594387</v>
       </c>
       <c r="R26" t="n">
-        <v>7183690</v>
+        <v>7183695</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3505,7 +3385,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3515,7 +3395,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,123 +3419,6 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>121515977</v>
-      </c>
-      <c r="B27" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Bullersjön, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>594385</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7183550</v>
-      </c>
-      <c r="S27" t="n">
-        <v>25</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2024-12-08</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2024-12-08</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
